--- a/数据库信息/模板/义务教育学校教职工绩效工资审批表.xlsx
+++ b/数据库信息/模板/义务教育学校教职工绩效工资审批表.xlsx
@@ -1,427 +1,230 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="22400" windowHeight="9870"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="22400" windowHeight="9870" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="57">
-  <si>
-    <t>义务教育学校教职工绩效工资审批表</t>
-  </si>
-  <si>
-    <t>填报单位：</t>
-  </si>
-  <si>
-    <t>太平镇中心学校</t>
-  </si>
-  <si>
-    <t>填报时间:</t>
-  </si>
-  <si>
-    <t>单位：</t>
-  </si>
-  <si>
-    <t>人、元</t>
-  </si>
-  <si>
-    <t>项  目</t>
-  </si>
-  <si>
-    <t>基础性工资</t>
-  </si>
-  <si>
-    <t>呈报单位意见</t>
-  </si>
-  <si>
-    <t>人数</t>
-  </si>
-  <si>
-    <t>月工资标准</t>
-  </si>
-  <si>
-    <t>小计</t>
-  </si>
-  <si>
-    <t>行政管理人员</t>
-  </si>
-  <si>
-    <t>1、副处级</t>
-  </si>
-  <si>
-    <t>据实填写，同意呈报。</t>
-  </si>
-  <si>
-    <t>2、正科级</t>
-  </si>
-  <si>
-    <t>（盖章）</t>
-  </si>
-  <si>
-    <t>3、副科级</t>
-  </si>
-  <si>
-    <t>4、科员级</t>
-  </si>
-  <si>
-    <t>5、办事员级</t>
-  </si>
-  <si>
-    <t>专业技术人员</t>
-  </si>
-  <si>
-    <t>教育局意见</t>
-  </si>
-  <si>
-    <t>1、正高级</t>
-  </si>
-  <si>
-    <t>2、高级教师</t>
-  </si>
-  <si>
-    <t>3、一级教师</t>
-  </si>
-  <si>
-    <t>4、二级教师</t>
-  </si>
-  <si>
-    <t>5、三级教师</t>
-  </si>
-  <si>
-    <t>工人</t>
-  </si>
-  <si>
-    <t>1、高级技师</t>
-  </si>
-  <si>
-    <t>2、技师</t>
-  </si>
-  <si>
-    <t>3、高级工</t>
-  </si>
-  <si>
-    <t>人事部门意见</t>
-  </si>
-  <si>
-    <t xml:space="preserve">    根据相关文件及有关规定，经审核，同意你单位：</t>
-  </si>
-  <si>
-    <t>4、中级工</t>
-  </si>
-  <si>
-    <t>基础性绩效工资</t>
-  </si>
-  <si>
-    <t>人</t>
-  </si>
-  <si>
-    <t>元；</t>
-  </si>
-  <si>
-    <t>5、初级工</t>
-  </si>
-  <si>
-    <t>生活补贴</t>
-  </si>
-  <si>
-    <t>6、普工</t>
-  </si>
-  <si>
-    <t>合计：</t>
-  </si>
-  <si>
-    <t>元</t>
-  </si>
-  <si>
-    <t>绩效工资合计</t>
-  </si>
-  <si>
-    <t>岗位设置遗留</t>
-  </si>
-  <si>
-    <t>元。</t>
-  </si>
-  <si>
-    <t>乡镇补贴合计</t>
-  </si>
-  <si>
-    <t>总计：</t>
-  </si>
-  <si>
-    <t>岗位设置
-遗留问题</t>
-  </si>
-  <si>
-    <t>李发金</t>
-  </si>
-  <si>
-    <t>无乡镇补贴</t>
-  </si>
-  <si>
-    <t>人：</t>
-  </si>
-  <si>
-    <t>柯坤</t>
-  </si>
-  <si>
-    <t>张照凯</t>
-  </si>
-  <si>
-    <t>退休干部</t>
-  </si>
-  <si>
-    <t>退休工人</t>
-  </si>
-  <si>
-    <t>离休干部</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-备注：
-1.退休教师死亡2人：赵明安、候兴志
-</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="6">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="yyyy&quot;年&quot;m&quot;月&quot;;@"/>
-    <numFmt numFmtId="177" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy&quot;年&quot;m&quot;月&quot;;@"/>
+    <numFmt numFmtId="165" formatCode="yyyy&quot;年&quot;m&quot;月&quot;d&quot;日&quot;;@"/>
   </numFmts>
   <fonts count="29">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <sz val="16"/>
     </font>
     <font>
-      <sz val="18"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <sz val="18"/>
     </font>
     <font>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <sz val="10"/>
     </font>
     <font>
-      <b/>
-      <sz val="10"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="10"/>
     </font>
     <font>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <sz val="11"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -613,7 +416,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="46">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -1188,515 +991,614 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="medium">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="medium">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="42" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="41" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="5" borderId="43" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="44" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="45" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="38" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="39" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="39" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="40" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="3" borderId="41" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="42" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="41" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="5" borderId="43" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="44" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="45" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="119">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+  <cellXfs count="141">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="centerContinuous" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="31" fontId="4" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="31" fontId="4" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="49">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="31" fontId="1" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="1" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="12" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="26" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="29" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="19" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="30" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="31" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="32" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="33" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="20" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="34" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="31" fontId="7" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="31" fontId="7" fillId="0" borderId="21" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="23" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="36" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="37" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="46" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="31" fontId="4" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="31" fontId="1" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="35" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="28" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="31" fontId="7" fillId="0" borderId="25" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="49" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="50">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1943,7 +1845,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="6"/>
       <tableStyleElement type="headerRow" dxfId="5"/>
       <tableStyleElement type="totalRow" dxfId="4"/>
@@ -1952,7 +1854,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="1"/>
       <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10">
       <tableStyleElement type="headerRow" dxfId="16"/>
       <tableStyleElement type="totalRow" dxfId="15"/>
       <tableStyleElement type="firstRowStripe" dxfId="14"/>
@@ -1965,11 +1867,74 @@
       <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -2221,696 +2186,798 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:W32"/>
-  <sheetFormatPr defaultColWidth="8.81818181818182" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="8.81818181818182" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.8181818181818" style="1" customWidth="1"/>
-    <col min="2" max="2" width="7.63636363636364" style="2" customWidth="1"/>
-    <col min="3" max="3" width="13.0363636363636" style="2" customWidth="1"/>
-    <col min="4" max="4" width="9.36363636363636" style="2" customWidth="1"/>
-    <col min="5" max="5" width="6.09090909090909" style="2" customWidth="1"/>
-    <col min="6" max="6" width="8.81818181818182" style="1"/>
-    <col min="7" max="7" width="17.6363636363636" style="1" customWidth="1"/>
-    <col min="8" max="8" width="5" style="1" customWidth="1"/>
-    <col min="9" max="9" width="3.90909090909091" style="1" customWidth="1"/>
-    <col min="10" max="10" width="11" style="1" customWidth="1"/>
-    <col min="11" max="11" width="8.63636363636364" style="1" customWidth="1"/>
-    <col min="12" max="13" width="8.81818181818182" style="1"/>
-    <col min="14" max="14" width="10.1818181818182" style="1" customWidth="1"/>
-    <col min="15" max="15" width="15.3636363636364" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.4545454545455" style="1"/>
-    <col min="17" max="16381" width="8.81818181818182" style="1"/>
-    <col min="16382" max="16384" width="8.81818181818182" style="3"/>
+    <col width="13.8181818181818" customWidth="1" style="13" min="1" max="1"/>
+    <col width="7.63636363636364" customWidth="1" style="38" min="2" max="2"/>
+    <col width="13.0363636363636" customWidth="1" style="38" min="3" max="3"/>
+    <col width="9.36363636363636" customWidth="1" style="38" min="4" max="4"/>
+    <col width="6.09090909090909" customWidth="1" style="38" min="5" max="5"/>
+    <col width="8.81818181818182" customWidth="1" style="13" min="6" max="6"/>
+    <col width="17.6363636363636" customWidth="1" style="13" min="7" max="7"/>
+    <col width="5" customWidth="1" style="13" min="8" max="8"/>
+    <col width="3.90909090909091" customWidth="1" style="13" min="9" max="9"/>
+    <col width="11" customWidth="1" style="13" min="10" max="10"/>
+    <col width="8.63636363636364" customWidth="1" style="13" min="11" max="11"/>
+    <col width="8.81818181818182" customWidth="1" style="13" min="12" max="13"/>
+    <col width="10.1818181818182" customWidth="1" style="13" min="14" max="14"/>
+    <col width="15.3636363636364" customWidth="1" style="13" min="15" max="15"/>
+    <col width="11.4545454545455" customWidth="1" style="13" min="16" max="16"/>
+    <col width="8.81818181818182" customWidth="1" style="13" min="17" max="16381"/>
+    <col width="8.81818181818182" customWidth="1" style="3" min="16382" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="27" customHeight="1" spans="1:23">
-      <c r="A1" s="4"/>
-      <c r="B1" s="5">
+    <row r="1" ht="27" customFormat="1" customHeight="1" s="13">
+      <c r="A1" s="4" t="n"/>
+      <c r="B1" s="119" t="n">
         <v>46170</v>
       </c>
-      <c r="C1" s="5"/>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="6" t="inlineStr">
+        <is>
+          <t>义务教育学校教职工绩效工资审批表</t>
+        </is>
+      </c>
+      <c r="E1" s="38" t="n"/>
+      <c r="G1" s="7" t="n"/>
+      <c r="H1" s="8" t="n"/>
+      <c r="I1" s="8" t="n"/>
+      <c r="J1" s="8" t="n"/>
+      <c r="K1" s="9" t="n"/>
+    </row>
+    <row r="2" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A2" s="13" t="inlineStr">
+        <is>
+          <t>填报单位：</t>
+        </is>
+      </c>
+      <c r="B2" s="38" t="inlineStr">
+        <is>
+          <t>太平镇中心学校</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>填报时间:</t>
+        </is>
+      </c>
+      <c r="G2" s="120" t="n">
+        <v>46140</v>
+      </c>
+      <c r="H2" s="11" t="inlineStr">
+        <is>
+          <t>单位：</t>
+        </is>
+      </c>
+      <c r="J2" s="13" t="inlineStr">
+        <is>
+          <t>人、元</t>
+        </is>
+      </c>
+      <c r="K2" s="13" t="n"/>
+    </row>
+    <row r="3" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A3" s="121" t="inlineStr">
+        <is>
+          <t>项  目</t>
+        </is>
+      </c>
+      <c r="B3" s="30" t="inlineStr">
+        <is>
+          <t>基础性工资</t>
+        </is>
+      </c>
+      <c r="C3" s="122" t="n"/>
+      <c r="D3" s="123" t="n"/>
+      <c r="E3" s="124" t="inlineStr">
+        <is>
+          <t>呈报单位意见</t>
+        </is>
+      </c>
+      <c r="F3" s="49" t="n"/>
+      <c r="G3" s="50" t="n"/>
+      <c r="H3" s="50" t="n"/>
+      <c r="I3" s="50" t="n"/>
+      <c r="J3" s="50" t="n"/>
+      <c r="K3" s="51" t="n"/>
+    </row>
+    <row r="4" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A4" s="125" t="n"/>
+      <c r="B4" s="23" t="inlineStr">
+        <is>
+          <t>人数</t>
+        </is>
+      </c>
+      <c r="C4" s="23" t="inlineStr">
+        <is>
+          <t>月工资标准</t>
+        </is>
+      </c>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>小计</t>
+        </is>
+      </c>
+      <c r="E4" s="126" t="n"/>
+      <c r="F4" s="41" t="n"/>
+      <c r="K4" s="42" t="n"/>
+    </row>
+    <row r="5" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>行政管理人员</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="126" t="n"/>
+      <c r="F5" s="41" t="n"/>
+      <c r="K5" s="42" t="n"/>
+    </row>
+    <row r="6" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A6" s="31" t="inlineStr">
+        <is>
+          <t>1、副处级</t>
+        </is>
+      </c>
+      <c r="B6" s="32" t="n"/>
+      <c r="C6" s="32" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="126" t="n"/>
+      <c r="F6" s="127" t="inlineStr">
+        <is>
+          <t>据实填写，同意呈报。</t>
+        </is>
+      </c>
+      <c r="K6" s="128" t="n"/>
+    </row>
+    <row r="7" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A7" s="31" t="inlineStr">
+        <is>
+          <t>2、正科级</t>
+        </is>
+      </c>
+      <c r="B7" s="32" t="n"/>
+      <c r="C7" s="32" t="n"/>
+      <c r="D7" s="33" t="n"/>
+      <c r="E7" s="126" t="n"/>
+      <c r="F7" s="129" t="inlineStr">
+        <is>
+          <t>（盖章）</t>
+        </is>
+      </c>
+      <c r="K7" s="128" t="n"/>
+    </row>
+    <row r="8" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>3、副科级</t>
+        </is>
+      </c>
+      <c r="B8" s="32" t="n"/>
+      <c r="C8" s="32" t="n"/>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="126" t="n"/>
+      <c r="F8" s="41" t="n"/>
+      <c r="K8" s="42" t="n"/>
+    </row>
+    <row r="9" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>4、科员级</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="n">
+        <v>5</v>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>1185</v>
+      </c>
+      <c r="D9" s="33" t="n">
+        <v>5925</v>
+      </c>
+      <c r="E9" s="126" t="n"/>
+      <c r="F9" s="41" t="n"/>
+      <c r="G9" s="13" t="n"/>
+      <c r="H9" s="13" t="n"/>
+      <c r="I9" s="13" t="n"/>
+      <c r="J9" s="13" t="n"/>
+      <c r="K9" s="42" t="n"/>
+    </row>
+    <row r="10" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A10" s="43" t="inlineStr">
+        <is>
+          <t>5、办事员级</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="n"/>
+      <c r="C10" s="23" t="n"/>
+      <c r="D10" s="24" t="n"/>
+      <c r="E10" s="125" t="n"/>
+      <c r="F10" s="130" t="n">
+        <v>46140</v>
+      </c>
+      <c r="G10" s="131" t="n"/>
+      <c r="H10" s="131" t="n"/>
+      <c r="I10" s="131" t="n"/>
+      <c r="J10" s="131" t="n"/>
+      <c r="K10" s="132" t="n"/>
+    </row>
+    <row r="11" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A11" s="48" t="inlineStr">
+        <is>
+          <t>专业技术人员</t>
+        </is>
+      </c>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="124" t="inlineStr">
+        <is>
+          <t>教育局意见</t>
+        </is>
+      </c>
+      <c r="F11" s="49" t="n"/>
+      <c r="G11" s="50" t="n"/>
+      <c r="H11" s="50" t="n"/>
+      <c r="I11" s="50" t="n"/>
+      <c r="J11" s="50" t="n"/>
+      <c r="K11" s="51" t="n"/>
+    </row>
+    <row r="12" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A12" s="31" t="inlineStr">
+        <is>
+          <t>1、正高级</t>
+        </is>
+      </c>
+      <c r="B12" s="32" t="n"/>
+      <c r="C12" s="40" t="n">
+        <v>1862</v>
+      </c>
+      <c r="D12" s="33" t="n">
         <v>0</v>
       </c>
-      <c r="E1" s="2"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="8"/>
-      <c r="I1" s="8"/>
-      <c r="J1" s="8"/>
-      <c r="K1" s="9"/>
-    </row>
-    <row r="2" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A2" s="1" t="s">
+      <c r="E12" s="126" t="n"/>
+      <c r="F12" s="41" t="n"/>
+      <c r="K12" s="42" t="n"/>
+    </row>
+    <row r="13" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A13" s="52" t="inlineStr">
+        <is>
+          <t>2、高级教师</t>
+        </is>
+      </c>
+      <c r="B13" s="53" t="n">
+        <v>44</v>
+      </c>
+      <c r="C13" s="54" t="n">
+        <v>1523</v>
+      </c>
+      <c r="D13" s="55" t="n">
+        <v>67012</v>
+      </c>
+      <c r="E13" s="126" t="n"/>
+      <c r="F13" s="41" t="n"/>
+      <c r="K13" s="42" t="n"/>
+      <c r="M13" s="56" t="n"/>
+      <c r="N13" s="56" t="n"/>
+      <c r="O13" s="56" t="n"/>
+      <c r="P13" s="56" t="n"/>
+      <c r="Q13" s="56" t="n"/>
+      <c r="R13" s="56" t="n"/>
+      <c r="S13" s="56" t="n"/>
+      <c r="T13" s="56" t="n"/>
+      <c r="U13" s="56" t="n"/>
+      <c r="V13" s="56" t="n"/>
+      <c r="W13" s="56" t="n"/>
+    </row>
+    <row r="14" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A14" s="57" t="inlineStr">
+        <is>
+          <t>3、一级教师</t>
+        </is>
+      </c>
+      <c r="B14" s="53" t="n">
+        <v>136</v>
+      </c>
+      <c r="C14" s="54" t="n">
+        <v>1309</v>
+      </c>
+      <c r="D14" s="55" t="n">
+        <v>178024</v>
+      </c>
+      <c r="E14" s="126" t="n"/>
+      <c r="F14" s="41" t="n"/>
+      <c r="K14" s="42" t="n"/>
+    </row>
+    <row r="15" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A15" s="57" t="inlineStr">
+        <is>
+          <t>4、二级教师</t>
+        </is>
+      </c>
+      <c r="B15" s="53" t="n">
+        <v>150</v>
+      </c>
+      <c r="C15" s="54" t="n">
+        <v>1241</v>
+      </c>
+      <c r="D15" s="55" t="n">
+        <v>186150</v>
+      </c>
+      <c r="E15" s="126" t="n"/>
+      <c r="F15" s="129" t="inlineStr">
+        <is>
+          <t>（盖章）</t>
+        </is>
+      </c>
+      <c r="K15" s="128" t="n"/>
+    </row>
+    <row r="16" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A16" s="58" t="inlineStr">
+        <is>
+          <t>5、三级教师</t>
+        </is>
+      </c>
+      <c r="B16" s="59" t="n">
+        <v>19</v>
+      </c>
+      <c r="C16" s="60" t="n">
+        <v>1128</v>
+      </c>
+      <c r="D16" s="99" t="n">
+        <v>21432</v>
+      </c>
+      <c r="E16" s="126" t="n"/>
+      <c r="F16" s="41" t="n"/>
+      <c r="K16" s="42" t="n"/>
+    </row>
+    <row r="17" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A17" s="62" t="inlineStr">
+        <is>
+          <t>工人</t>
+        </is>
+      </c>
+      <c r="B17" s="63" t="n"/>
+      <c r="C17" s="63" t="n"/>
+      <c r="D17" s="64" t="n"/>
+      <c r="E17" s="126" t="n"/>
+      <c r="F17" s="41" t="n"/>
+      <c r="K17" s="42" t="n"/>
+    </row>
+    <row r="18" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A18" s="52" t="inlineStr">
+        <is>
+          <t>1、高级技师</t>
+        </is>
+      </c>
+      <c r="B18" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="55" t="n"/>
+      <c r="E18" s="126" t="n"/>
+      <c r="F18" s="41" t="n"/>
+      <c r="K18" s="42" t="n"/>
+    </row>
+    <row r="19" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A19" s="52" t="inlineStr">
+        <is>
+          <t>2、技师</t>
+        </is>
+      </c>
+      <c r="B19" s="53" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="54" t="n">
+        <v>1331</v>
+      </c>
+      <c r="D19" s="55" t="n">
+        <v>2662</v>
+      </c>
+      <c r="E19" s="125" t="n"/>
+      <c r="F19" s="133" t="n">
+        <v>46141</v>
+      </c>
+      <c r="G19" s="131" t="n"/>
+      <c r="H19" s="131" t="n"/>
+      <c r="I19" s="131" t="n"/>
+      <c r="J19" s="131" t="n"/>
+      <c r="K19" s="132" t="n"/>
+    </row>
+    <row r="20" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A20" s="52" t="inlineStr">
+        <is>
+          <t>3、高级工</t>
+        </is>
+      </c>
+      <c r="B20" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="54" t="n">
+        <v>1219</v>
+      </c>
+      <c r="D20" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="134" t="inlineStr">
+        <is>
+          <t>人事部门意见</t>
+        </is>
+      </c>
+      <c r="F20" s="135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">    根据相关文件及有关规定，经审核，同意你单位：</t>
+        </is>
+      </c>
+      <c r="G20" s="136" t="n"/>
+      <c r="H20" s="136" t="n"/>
+      <c r="I20" s="136" t="n"/>
+      <c r="J20" s="136" t="n"/>
+      <c r="K20" s="137" t="n"/>
+    </row>
+    <row r="21" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A21" s="52" t="inlineStr">
+        <is>
+          <t>4、中级工</t>
+        </is>
+      </c>
+      <c r="B21" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="54" t="n">
+        <v>1185</v>
+      </c>
+      <c r="D21" s="55" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="126" t="n"/>
+      <c r="F21" s="73" t="inlineStr">
+        <is>
+          <t>基础性绩效工资</t>
+        </is>
+      </c>
+      <c r="H21" s="75" t="n">
+        <v>357</v>
+      </c>
+      <c r="I21" s="75" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="J21" s="75" t="n">
+        <v>462311</v>
+      </c>
+      <c r="K21" s="76" t="inlineStr">
+        <is>
+          <t>元；</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A22" s="52" t="inlineStr">
+        <is>
+          <t>5、初级工</t>
+        </is>
+      </c>
+      <c r="B22" s="53" t="n">
         <v>1</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="C22" s="54" t="n">
+        <v>1106</v>
+      </c>
+      <c r="D22" s="55" t="n">
+        <v>1106</v>
+      </c>
+      <c r="E22" s="126" t="n"/>
+      <c r="F22" s="73" t="inlineStr">
+        <is>
+          <t>生活补贴</t>
+        </is>
+      </c>
+      <c r="H22" s="75" t="n">
+        <v>356</v>
+      </c>
+      <c r="I22" s="75" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="J22" s="75" t="n">
+        <v>124600</v>
+      </c>
+      <c r="K22" s="76" t="inlineStr">
+        <is>
+          <t>元；</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A23" s="58" t="inlineStr">
+        <is>
+          <t>6、普工</t>
+        </is>
+      </c>
+      <c r="B23" s="59" t="n">
+        <v>0</v>
+      </c>
+      <c r="C23" s="60" t="n">
+        <v>1106</v>
+      </c>
+      <c r="D23" s="99" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="126" t="n"/>
+      <c r="F23" s="77" t="inlineStr">
+        <is>
+          <t>合计：</t>
+        </is>
+      </c>
+      <c r="J23" s="79" t="n">
+        <v>586911</v>
+      </c>
+      <c r="K23" s="80" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A24" s="81" t="inlineStr">
+        <is>
+          <t>绩效工资合计</t>
+        </is>
+      </c>
+      <c r="B24" s="82" t="n">
+        <v>357</v>
+      </c>
+      <c r="C24" s="82" t="n"/>
+      <c r="D24" s="83" t="n">
+        <v>462311</v>
+      </c>
+      <c r="E24" s="126" t="n"/>
+      <c r="F24" s="73" t="inlineStr">
+        <is>
+          <t>岗位设置遗留</t>
+        </is>
+      </c>
+      <c r="H24" s="75" t="n">
         <v>2</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="11" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12">
-        <v>46140</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="I2" s="11"/>
-      <c r="J2" s="13" t="s">
-        <v>5</v>
-      </c>
-      <c r="K2" s="13"/>
-    </row>
-    <row r="3" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A3" s="14" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="15" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" s="16"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="18" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="19"/>
-      <c r="G3" s="20"/>
-      <c r="H3" s="20"/>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="21"/>
-    </row>
-    <row r="4" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A4" s="22"/>
-      <c r="B4" s="23" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="D4" s="24" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" s="25"/>
-      <c r="F4" s="26"/>
-      <c r="K4" s="27"/>
-    </row>
-    <row r="5" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A5" s="28" t="s">
-        <v>12</v>
-      </c>
-      <c r="B5" s="29"/>
-      <c r="C5" s="29"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="26"/>
-      <c r="K5" s="27"/>
-    </row>
-    <row r="6" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A6" s="31" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="32"/>
-      <c r="C6" s="32"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="25"/>
-      <c r="F6" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="G6" s="35"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="35"/>
-      <c r="J6" s="35"/>
-      <c r="K6" s="36"/>
-    </row>
-    <row r="7" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A7" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="B7" s="32"/>
-      <c r="C7" s="32"/>
-      <c r="D7" s="33"/>
-      <c r="E7" s="25"/>
-      <c r="F7" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="G7" s="38"/>
-      <c r="H7" s="38"/>
-      <c r="I7" s="38"/>
-      <c r="J7" s="38"/>
-      <c r="K7" s="39"/>
-    </row>
-    <row r="8" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A8" s="31" t="s">
-        <v>17</v>
-      </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="25"/>
-      <c r="F8" s="26"/>
-      <c r="K8" s="27"/>
-    </row>
-    <row r="9" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A9" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" s="32">
-        <v>5</v>
-      </c>
-      <c r="C9" s="40">
-        <v>1185</v>
-      </c>
-      <c r="D9" s="33">
-        <v>5925</v>
-      </c>
-      <c r="E9" s="25"/>
-      <c r="F9" s="41"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
-      <c r="J9" s="13"/>
-      <c r="K9" s="42"/>
-    </row>
-    <row r="10" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A10" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="B10" s="23"/>
-      <c r="C10" s="23"/>
-      <c r="D10" s="24"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="45">
-        <v>46140</v>
-      </c>
-      <c r="G10" s="46"/>
-      <c r="H10" s="46"/>
-      <c r="I10" s="46"/>
-      <c r="J10" s="46"/>
-      <c r="K10" s="47"/>
-    </row>
-    <row r="11" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A11" s="48" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="29"/>
-      <c r="C11" s="29"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="F11" s="49"/>
-      <c r="G11" s="50"/>
-      <c r="H11" s="50"/>
-      <c r="I11" s="50"/>
-      <c r="J11" s="50"/>
-      <c r="K11" s="51"/>
-    </row>
-    <row r="12" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A12" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="40">
-        <v>1862</v>
-      </c>
-      <c r="D12" s="33">
-        <v>0</v>
-      </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="26"/>
-      <c r="K12" s="27"/>
-    </row>
-    <row r="13" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A13" s="52" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="53">
-        <v>44</v>
-      </c>
-      <c r="C13" s="54">
-        <v>1523</v>
-      </c>
-      <c r="D13" s="55">
-        <v>67012</v>
-      </c>
-      <c r="E13" s="25"/>
-      <c r="F13" s="26"/>
-      <c r="K13" s="27"/>
-      <c r="M13" s="56"/>
-      <c r="N13" s="56"/>
-      <c r="O13" s="56"/>
-      <c r="P13" s="56"/>
-      <c r="Q13" s="56"/>
-      <c r="R13" s="56"/>
-      <c r="S13" s="56"/>
-      <c r="T13" s="56"/>
-      <c r="U13" s="56"/>
-      <c r="V13" s="56"/>
-      <c r="W13" s="56"/>
-    </row>
-    <row r="14" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A14" s="57" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="53">
-        <v>136</v>
-      </c>
-      <c r="C14" s="54">
-        <v>1309</v>
-      </c>
-      <c r="D14" s="55">
-        <v>178024</v>
-      </c>
-      <c r="E14" s="25"/>
-      <c r="F14" s="26"/>
-      <c r="K14" s="27"/>
-    </row>
-    <row r="15" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A15" s="57" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="53">
-        <v>150</v>
-      </c>
-      <c r="C15" s="54">
-        <v>1241</v>
-      </c>
-      <c r="D15" s="55">
-        <v>186150</v>
-      </c>
-      <c r="E15" s="25"/>
-      <c r="F15" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="G15" s="10"/>
-      <c r="H15" s="10"/>
-      <c r="I15" s="10"/>
-      <c r="J15" s="10"/>
-      <c r="K15" s="39"/>
-    </row>
-    <row r="16" s="1" customFormat="1" ht="25" customHeight="1" spans="1:23">
-      <c r="A16" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="59">
-        <v>19</v>
-      </c>
-      <c r="C16" s="60">
-        <v>1128</v>
-      </c>
-      <c r="D16" s="61">
-        <v>21432</v>
-      </c>
-      <c r="E16" s="25"/>
-      <c r="F16" s="26"/>
-      <c r="K16" s="27"/>
-    </row>
-    <row r="17" s="1" customFormat="1" ht="25" customHeight="1" spans="1:11">
-      <c r="A17" s="62" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="63"/>
-      <c r="C17" s="63"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="25"/>
-      <c r="F17" s="26"/>
-      <c r="K17" s="27"/>
-    </row>
-    <row r="18" s="1" customFormat="1" ht="25" customHeight="1" spans="1:11">
-      <c r="A18" s="52" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="53">
-        <v>0</v>
-      </c>
-      <c r="C18" s="53"/>
-      <c r="D18" s="55"/>
-      <c r="E18" s="25"/>
-      <c r="F18" s="26"/>
-      <c r="K18" s="27"/>
-    </row>
-    <row r="19" s="1" customFormat="1" ht="25" customHeight="1" spans="1:11">
-      <c r="A19" s="52" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="53">
-        <v>2</v>
-      </c>
-      <c r="C19" s="54">
-        <v>1331</v>
-      </c>
-      <c r="D19" s="55">
-        <v>2662</v>
-      </c>
-      <c r="E19" s="44"/>
-      <c r="F19" s="65">
-        <v>46141</v>
-      </c>
-      <c r="G19" s="66"/>
-      <c r="H19" s="66"/>
-      <c r="I19" s="66"/>
-      <c r="J19" s="66"/>
-      <c r="K19" s="67"/>
-    </row>
-    <row r="20" s="1" customFormat="1" ht="25" customHeight="1" spans="1:11">
-      <c r="A20" s="52" t="s">
-        <v>30</v>
-      </c>
-      <c r="B20" s="53">
-        <v>0</v>
-      </c>
-      <c r="C20" s="54">
-        <v>1219</v>
-      </c>
-      <c r="D20" s="55">
-        <v>0</v>
-      </c>
-      <c r="E20" s="68" t="s">
-        <v>31</v>
-      </c>
-      <c r="F20" s="69" t="s">
-        <v>32</v>
-      </c>
-      <c r="G20" s="70"/>
-      <c r="H20" s="70"/>
-      <c r="I20" s="70"/>
-      <c r="J20" s="70"/>
-      <c r="K20" s="71"/>
-    </row>
-    <row r="21" s="1" customFormat="1" ht="25" customHeight="1" spans="1:11">
-      <c r="A21" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="B21" s="53">
-        <v>0</v>
-      </c>
-      <c r="C21" s="54">
-        <v>1185</v>
-      </c>
-      <c r="D21" s="55">
-        <v>0</v>
-      </c>
-      <c r="E21" s="72"/>
-      <c r="F21" s="73" t="s">
-        <v>34</v>
-      </c>
-      <c r="G21" s="74"/>
-      <c r="H21" s="75">
-        <v>357</v>
-      </c>
-      <c r="I21" s="75" t="s">
-        <v>35</v>
-      </c>
-      <c r="J21" s="75">
-        <v>462311</v>
-      </c>
-      <c r="K21" s="76" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="22" s="1" customFormat="1" ht="25" customHeight="1" spans="1:11">
-      <c r="A22" s="52" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="53">
-        <v>1</v>
-      </c>
-      <c r="C22" s="54">
-        <v>1106</v>
-      </c>
-      <c r="D22" s="55">
-        <v>1106</v>
-      </c>
-      <c r="E22" s="72"/>
-      <c r="F22" s="73" t="s">
-        <v>38</v>
-      </c>
-      <c r="G22" s="74"/>
-      <c r="H22" s="75">
+      <c r="I24" s="75" t="inlineStr">
+        <is>
+          <t>人</t>
+        </is>
+      </c>
+      <c r="J24" s="75" t="n">
+        <v>675.24</v>
+      </c>
+      <c r="K24" s="76" t="inlineStr">
+        <is>
+          <t>元。</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A25" s="84" t="inlineStr">
+        <is>
+          <t>乡镇补贴合计</t>
+        </is>
+      </c>
+      <c r="B25" s="85" t="n">
         <v>356</v>
       </c>
-      <c r="I22" s="75" t="s">
-        <v>35</v>
-      </c>
-      <c r="J22" s="75">
+      <c r="C25" s="85" t="n">
+        <v>350</v>
+      </c>
+      <c r="D25" s="86" t="n">
         <v>124600</v>
       </c>
-      <c r="K22" s="76" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" s="1" customFormat="1" ht="25" customHeight="1" spans="1:11">
-      <c r="A23" s="58" t="s">
-        <v>39</v>
-      </c>
-      <c r="B23" s="59">
-        <v>0</v>
-      </c>
-      <c r="C23" s="60">
-        <v>1106</v>
-      </c>
-      <c r="D23" s="61">
-        <v>0</v>
-      </c>
-      <c r="E23" s="72"/>
-      <c r="F23" s="77" t="s">
-        <v>40</v>
-      </c>
-      <c r="G23" s="78"/>
-      <c r="H23" s="78"/>
-      <c r="I23" s="78"/>
-      <c r="J23" s="79">
-        <v>586911</v>
-      </c>
-      <c r="K23" s="80" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="24" s="1" customFormat="1" ht="25" customHeight="1" spans="1:11">
-      <c r="A24" s="81" t="s">
-        <v>42</v>
-      </c>
-      <c r="B24" s="82">
-        <v>357</v>
-      </c>
-      <c r="C24" s="82"/>
-      <c r="D24" s="83">
-        <v>462311</v>
-      </c>
-      <c r="E24" s="72"/>
-      <c r="F24" s="73" t="s">
-        <v>43</v>
-      </c>
-      <c r="G24" s="74"/>
-      <c r="H24" s="75">
-        <v>2</v>
-      </c>
-      <c r="I24" s="75" t="s">
-        <v>35</v>
-      </c>
-      <c r="J24" s="75">
-        <v>675.24</v>
-      </c>
-      <c r="K24" s="76" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="25" s="1" customFormat="1" ht="25" customHeight="1" spans="1:11">
-      <c r="A25" s="84" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="85">
-        <v>356</v>
-      </c>
-      <c r="C25" s="85">
-        <v>350</v>
-      </c>
-      <c r="D25" s="86">
-        <v>124600</v>
-      </c>
-      <c r="E25" s="72"/>
-      <c r="F25" s="77" t="s">
-        <v>46</v>
-      </c>
-      <c r="G25" s="78"/>
-      <c r="H25" s="78"/>
-      <c r="I25" s="78"/>
+      <c r="E25" s="126" t="n"/>
+      <c r="F25" s="77" t="inlineStr">
+        <is>
+          <t>总计：</t>
+        </is>
+      </c>
       <c r="J25" s="79">
         <f>J23+J24</f>
-        <v>587586.24</v>
-      </c>
-      <c r="K25" s="80" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" s="1" customFormat="1" ht="37" customHeight="1" spans="1:11">
-      <c r="A26" s="87" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="88" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="89">
+        <v/>
+      </c>
+      <c r="K25" s="80" t="inlineStr">
+        <is>
+          <t>元</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="37" customFormat="1" customHeight="1" s="13">
+      <c r="A26" s="87" t="inlineStr">
+        <is>
+          <t>岗位设置
+遗留问题</t>
+        </is>
+      </c>
+      <c r="B26" s="88" t="inlineStr">
+        <is>
+          <t>李发金</t>
+        </is>
+      </c>
+      <c r="C26" s="89" t="n">
         <v>321.3</v>
       </c>
-      <c r="D26" s="90">
+      <c r="D26" s="90" t="n">
         <v>321.3</v>
       </c>
-      <c r="E26" s="91"/>
-      <c r="F26" s="73" t="s">
-        <v>49</v>
-      </c>
-      <c r="G26" s="74"/>
-      <c r="H26" s="75">
+      <c r="E26" s="126" t="n"/>
+      <c r="F26" s="73" t="inlineStr">
+        <is>
+          <t>无乡镇补贴</t>
+        </is>
+      </c>
+      <c r="H26" s="75" t="n">
         <v>1</v>
       </c>
-      <c r="I26" s="92" t="s">
-        <v>50</v>
-      </c>
-      <c r="J26" s="75" t="s">
-        <v>51</v>
-      </c>
-      <c r="K26" s="76"/>
-    </row>
-    <row r="27" s="1" customFormat="1" ht="37" customHeight="1" spans="1:11">
-      <c r="A27" s="93" t="s">
-        <v>47</v>
-      </c>
-      <c r="B27" s="94" t="s">
-        <v>52</v>
-      </c>
-      <c r="C27" s="95">
+      <c r="I26" s="92" t="inlineStr">
+        <is>
+          <t>人：</t>
+        </is>
+      </c>
+      <c r="J26" s="75" t="inlineStr">
+        <is>
+          <t>柯坤</t>
+        </is>
+      </c>
+      <c r="K26" s="76" t="n"/>
+    </row>
+    <row r="27" ht="37" customFormat="1" customHeight="1" s="13">
+      <c r="A27" s="104" t="inlineStr">
+        <is>
+          <t>岗位设置
+遗留问题</t>
+        </is>
+      </c>
+      <c r="B27" s="94" t="inlineStr">
+        <is>
+          <t>张照凯</t>
+        </is>
+      </c>
+      <c r="C27" s="105" t="n">
         <v>353.94</v>
       </c>
-      <c r="D27" s="96">
+      <c r="D27" s="96" t="n">
         <v>353.94</v>
       </c>
-      <c r="E27" s="91"/>
-      <c r="F27" s="77"/>
-      <c r="G27" s="78"/>
-      <c r="H27" s="78"/>
-      <c r="I27" s="78"/>
-      <c r="J27" s="79"/>
-      <c r="K27" s="80"/>
-    </row>
-    <row r="28" s="1" customFormat="1" ht="36" customHeight="1" spans="1:11">
-      <c r="A28" s="97" t="s">
-        <v>47</v>
-      </c>
-      <c r="B28" s="98">
+      <c r="E27" s="126" t="n"/>
+      <c r="F27" s="77" t="n"/>
+      <c r="J27" s="79" t="n"/>
+      <c r="K27" s="80" t="n"/>
+    </row>
+    <row r="28" ht="36" customFormat="1" customHeight="1" s="13">
+      <c r="A28" s="97" t="inlineStr">
+        <is>
+          <t>岗位设置
+遗留问题</t>
+        </is>
+      </c>
+      <c r="B28" s="98" t="n">
         <v>2</v>
       </c>
-      <c r="C28" s="59"/>
-      <c r="D28" s="99">
+      <c r="C28" s="59" t="n"/>
+      <c r="D28" s="99" t="n">
         <v>675.24</v>
       </c>
-      <c r="E28" s="91"/>
-      <c r="F28" s="26"/>
-      <c r="K28" s="27"/>
-    </row>
-    <row r="29" s="1" customFormat="1" ht="25" customHeight="1" spans="1:11">
-      <c r="A29" s="100" t="s">
-        <v>53</v>
-      </c>
-      <c r="B29" s="101">
+      <c r="E28" s="126" t="n"/>
+      <c r="F28" s="41" t="n"/>
+      <c r="K28" s="42" t="n"/>
+    </row>
+    <row r="29" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A29" s="100" t="inlineStr">
+        <is>
+          <t>退休干部</t>
+        </is>
+      </c>
+      <c r="B29" s="101" t="n">
         <v>447</v>
       </c>
-      <c r="C29" s="102"/>
-      <c r="D29" s="103"/>
-      <c r="E29" s="72"/>
-      <c r="F29" s="26"/>
-      <c r="K29" s="27"/>
-    </row>
-    <row r="30" s="1" customFormat="1" ht="25" customHeight="1" spans="1:11">
-      <c r="A30" s="104" t="s">
-        <v>54</v>
-      </c>
-      <c r="B30" s="105">
+      <c r="C29" s="102" t="n"/>
+      <c r="D29" s="103" t="n"/>
+      <c r="E29" s="126" t="n"/>
+      <c r="F29" s="41" t="n"/>
+      <c r="K29" s="42" t="n"/>
+    </row>
+    <row r="30" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A30" s="104" t="inlineStr">
+        <is>
+          <t>退休工人</t>
+        </is>
+      </c>
+      <c r="B30" s="105" t="n">
         <v>2</v>
       </c>
-      <c r="C30" s="53"/>
-      <c r="D30" s="106"/>
-      <c r="E30" s="72"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="75"/>
-      <c r="I30" s="75"/>
-      <c r="J30" s="107"/>
-      <c r="K30" s="108"/>
-    </row>
-    <row r="31" s="1" customFormat="1" ht="25" customHeight="1" spans="1:11">
-      <c r="A31" s="109" t="s">
-        <v>55</v>
-      </c>
-      <c r="B31" s="98">
+      <c r="C30" s="53" t="n"/>
+      <c r="D30" s="106" t="n"/>
+      <c r="E30" s="126" t="n"/>
+      <c r="F30" s="73" t="n"/>
+      <c r="H30" s="75" t="n"/>
+      <c r="I30" s="75" t="n"/>
+      <c r="J30" s="108" t="n"/>
+      <c r="K30" s="128" t="n"/>
+    </row>
+    <row r="31" ht="25" customFormat="1" customHeight="1" s="13">
+      <c r="A31" s="109" t="inlineStr">
+        <is>
+          <t>离休干部</t>
+        </is>
+      </c>
+      <c r="B31" s="98" t="n">
         <v>1</v>
       </c>
-      <c r="C31" s="59"/>
-      <c r="D31" s="110"/>
-      <c r="E31" s="111"/>
-      <c r="F31" s="112">
+      <c r="C31" s="59" t="n"/>
+      <c r="D31" s="110" t="n"/>
+      <c r="E31" s="125" t="n"/>
+      <c r="F31" s="138" t="n">
         <v>46142</v>
       </c>
-      <c r="G31" s="113"/>
-      <c r="H31" s="113"/>
-      <c r="I31" s="113"/>
-      <c r="J31" s="113"/>
-      <c r="K31" s="114"/>
-    </row>
-    <row r="32" s="1" customFormat="1" ht="130" customHeight="1" spans="1:11">
-      <c r="A32" s="115" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" s="116"/>
-      <c r="C32" s="116"/>
-      <c r="D32" s="116"/>
-      <c r="E32" s="116"/>
-      <c r="F32" s="117"/>
-      <c r="G32" s="117"/>
-      <c r="H32" s="117"/>
-      <c r="I32" s="117"/>
-      <c r="J32" s="117"/>
-      <c r="K32" s="118"/>
+      <c r="G31" s="131" t="n"/>
+      <c r="H31" s="131" t="n"/>
+      <c r="I31" s="131" t="n"/>
+      <c r="J31" s="131" t="n"/>
+      <c r="K31" s="132" t="n"/>
+    </row>
+    <row r="32" ht="130" customFormat="1" customHeight="1" s="13">
+      <c r="A32" s="115" t="inlineStr">
+        <is>
+          <t xml:space="preserve">
+备注：
+</t>
+        </is>
+      </c>
+      <c r="B32" s="139" t="n"/>
+      <c r="C32" s="139" t="n"/>
+      <c r="D32" s="139" t="n"/>
+      <c r="E32" s="139" t="n"/>
+      <c r="F32" s="139" t="n"/>
+      <c r="G32" s="139" t="n"/>
+      <c r="H32" s="139" t="n"/>
+      <c r="I32" s="139" t="n"/>
+      <c r="J32" s="139" t="n"/>
+      <c r="K32" s="140" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="F20:K20"/>
+    <mergeCell ref="F27:I27"/>
+    <mergeCell ref="E3:E10"/>
+    <mergeCell ref="E11:E19"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="J30:K30"/>
+    <mergeCell ref="F24:G24"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="F31:K31"/>
+    <mergeCell ref="F25:I25"/>
     <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="E20:E31"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="H2:I2"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A32:K32"/>
     <mergeCell ref="B3:D3"/>
+    <mergeCell ref="F19:K19"/>
+    <mergeCell ref="F10:K10"/>
     <mergeCell ref="F6:K6"/>
     <mergeCell ref="F7:K7"/>
-    <mergeCell ref="F10:K10"/>
+    <mergeCell ref="F23:I23"/>
+    <mergeCell ref="B2:D2"/>
     <mergeCell ref="F15:K15"/>
-    <mergeCell ref="F19:K19"/>
-    <mergeCell ref="F20:K20"/>
-    <mergeCell ref="F21:G21"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F23:I23"/>
-    <mergeCell ref="F24:G24"/>
-    <mergeCell ref="F25:I25"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F27:I27"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="J30:K30"/>
-    <mergeCell ref="F31:K31"/>
-    <mergeCell ref="A32:K32"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="E3:E10"/>
-    <mergeCell ref="E11:E19"/>
-    <mergeCell ref="E20:E31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" scale="76" orientation="portrait"/>
-  <headerFooter/>
+  <pageSetup orientation="portrait" paperSize="9" scale="76"/>
 </worksheet>
 </file>
--- a/数据库信息/模板/义务教育学校教职工绩效工资审批表.xlsx
+++ b/数据库信息/模板/义务教育学校教职工绩效工资审批表.xlsx
@@ -2400,9 +2400,7 @@
       <c r="C10" s="23" t="n"/>
       <c r="D10" s="24" t="n"/>
       <c r="E10" s="125" t="n"/>
-      <c r="F10" s="130" t="n">
-        <v>46140</v>
-      </c>
+      <c r="F10" s="130" t="n"/>
       <c r="G10" s="131" t="n"/>
       <c r="H10" s="131" t="n"/>
       <c r="I10" s="131" t="n"/>
@@ -2582,9 +2580,7 @@
         <v>2662</v>
       </c>
       <c r="E19" s="125" t="n"/>
-      <c r="F19" s="133" t="n">
-        <v>46141</v>
-      </c>
+      <c r="F19" s="133" t="n"/>
       <c r="G19" s="131" t="n"/>
       <c r="H19" s="131" t="n"/>
       <c r="I19" s="131" t="n"/>
@@ -2920,9 +2916,7 @@
       <c r="C31" s="59" t="n"/>
       <c r="D31" s="110" t="n"/>
       <c r="E31" s="125" t="n"/>
-      <c r="F31" s="138" t="n">
-        <v>46142</v>
-      </c>
+      <c r="F31" s="138" t="n"/>
       <c r="G31" s="131" t="n"/>
       <c r="H31" s="131" t="n"/>
       <c r="I31" s="131" t="n"/>
